--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072495</v>
+        <v>121072503</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545810</v>
+        <v>545872</v>
       </c>
       <c r="R2" t="n">
-        <v>7206003</v>
+        <v>7206105</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072500</v>
+        <v>121072501</v>
       </c>
       <c r="B3" t="n">
-        <v>90701</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545847</v>
+        <v>545845</v>
       </c>
       <c r="R3" t="n">
-        <v>7206036</v>
+        <v>7206038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072509</v>
+        <v>121072488</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545888</v>
+        <v>545768</v>
       </c>
       <c r="R4" t="n">
-        <v>7206177</v>
+        <v>7205889</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072505</v>
+        <v>121072500</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545867</v>
+        <v>545847</v>
       </c>
       <c r="R5" t="n">
-        <v>7206116</v>
+        <v>7206036</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072497</v>
+        <v>121072496</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545823</v>
+        <v>545822</v>
       </c>
       <c r="R6" t="n">
-        <v>7206018</v>
+        <v>7206019</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072501</v>
+        <v>121072510</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545845</v>
+        <v>545889</v>
       </c>
       <c r="R7" t="n">
-        <v>7206038</v>
+        <v>7206177</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072488</v>
+        <v>121072495</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545768</v>
+        <v>545810</v>
       </c>
       <c r="R8" t="n">
-        <v>7205889</v>
+        <v>7206003</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072489</v>
+        <v>121072490</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,34 +1485,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545766</v>
+        <v>545753</v>
       </c>
       <c r="R9" t="n">
-        <v>7205891</v>
+        <v>7205958</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072499</v>
+        <v>121072509</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545838</v>
+        <v>545888</v>
       </c>
       <c r="R10" t="n">
-        <v>7206020</v>
+        <v>7206177</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072503</v>
+        <v>121072504</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545872</v>
+        <v>545873</v>
       </c>
       <c r="R11" t="n">
-        <v>7206105</v>
+        <v>7206150</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072508</v>
+        <v>121072506</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,7 +1850,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1845,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545887</v>
+        <v>545865</v>
       </c>
       <c r="R12" t="n">
-        <v>7206178</v>
+        <v>7206180</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072507</v>
+        <v>121072491</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545862</v>
+        <v>545799</v>
       </c>
       <c r="R13" t="n">
-        <v>7206181</v>
+        <v>7205964</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072490</v>
+        <v>121072507</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,43 +2059,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545753</v>
+        <v>545862</v>
       </c>
       <c r="R14" t="n">
-        <v>7205958</v>
+        <v>7206181</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072496</v>
+        <v>121072508</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545822</v>
+        <v>545887</v>
       </c>
       <c r="R15" t="n">
-        <v>7206019</v>
+        <v>7206178</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072506</v>
+        <v>121072492</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>79683</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,39 +2288,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545865</v>
+        <v>545810</v>
       </c>
       <c r="R16" t="n">
-        <v>7206180</v>
+        <v>7206003</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072492</v>
+        <v>121072497</v>
       </c>
       <c r="B17" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545810</v>
+        <v>545823</v>
       </c>
       <c r="R17" t="n">
-        <v>7206003</v>
+        <v>7206018</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072498</v>
+        <v>121072494</v>
       </c>
       <c r="B18" t="n">
-        <v>94474</v>
+        <v>79711</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,21 +2512,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545838</v>
+        <v>545810</v>
       </c>
       <c r="R18" t="n">
-        <v>7206020</v>
+        <v>7206003</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072510</v>
+        <v>121072489</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545889</v>
+        <v>545766</v>
       </c>
       <c r="R19" t="n">
-        <v>7206177</v>
+        <v>7205891</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072494</v>
+        <v>121072498</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>94484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545810</v>
+        <v>545838</v>
       </c>
       <c r="R20" t="n">
-        <v>7206003</v>
+        <v>7206020</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,7 +2835,7 @@
         <v>121072502</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072504</v>
+        <v>121072505</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545873</v>
+        <v>545867</v>
       </c>
       <c r="R22" t="n">
-        <v>7206150</v>
+        <v>7206116</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072491</v>
+        <v>121072499</v>
       </c>
       <c r="B23" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545799</v>
+        <v>545838</v>
       </c>
       <c r="R23" t="n">
-        <v>7205964</v>
+        <v>7206020</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072496</v>
+        <v>121072510</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545822</v>
+        <v>545889</v>
       </c>
       <c r="R6" t="n">
-        <v>7206019</v>
+        <v>7206177</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072510</v>
+        <v>121072496</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545889</v>
+        <v>545822</v>
       </c>
       <c r="R7" t="n">
-        <v>7206177</v>
+        <v>7206019</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072503</v>
+        <v>121072509</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545872</v>
+        <v>545888</v>
       </c>
       <c r="R2" t="n">
-        <v>7206105</v>
+        <v>7206177</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072501</v>
+        <v>121072497</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545845</v>
+        <v>545823</v>
       </c>
       <c r="R3" t="n">
-        <v>7206038</v>
+        <v>7206018</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072500</v>
+        <v>121072499</v>
       </c>
       <c r="B5" t="n">
-        <v>90711</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545847</v>
+        <v>545838</v>
       </c>
       <c r="R5" t="n">
-        <v>7206036</v>
+        <v>7206020</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072510</v>
+        <v>121072501</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545889</v>
+        <v>545845</v>
       </c>
       <c r="R6" t="n">
-        <v>7206177</v>
+        <v>7206038</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072496</v>
+        <v>121072500</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90711</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545822</v>
+        <v>545847</v>
       </c>
       <c r="R7" t="n">
-        <v>7206019</v>
+        <v>7206036</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072495</v>
+        <v>121072490</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545810</v>
+        <v>545753</v>
       </c>
       <c r="R8" t="n">
-        <v>7206003</v>
+        <v>7205958</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072490</v>
+        <v>121072505</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,43 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545753</v>
+        <v>545867</v>
       </c>
       <c r="R9" t="n">
-        <v>7205958</v>
+        <v>7206116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072509</v>
+        <v>121072503</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545888</v>
+        <v>545872</v>
       </c>
       <c r="R10" t="n">
-        <v>7206177</v>
+        <v>7206105</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072504</v>
+        <v>121072496</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1713,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545873</v>
+        <v>545822</v>
       </c>
       <c r="R11" t="n">
-        <v>7206150</v>
+        <v>7206019</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072506</v>
+        <v>121072498</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>94484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,43 +1826,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545865</v>
+        <v>545838</v>
       </c>
       <c r="R12" t="n">
-        <v>7206180</v>
+        <v>7206020</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072491</v>
+        <v>121072507</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545799</v>
+        <v>545862</v>
       </c>
       <c r="R13" t="n">
-        <v>7205964</v>
+        <v>7206181</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,7 +2038,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072507</v>
+        <v>121072489</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2083,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545862</v>
+        <v>545766</v>
       </c>
       <c r="R14" t="n">
-        <v>7206181</v>
+        <v>7205891</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072508</v>
+        <v>121072510</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,39 +2166,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545887</v>
+        <v>545889</v>
       </c>
       <c r="R15" t="n">
-        <v>7206178</v>
+        <v>7206177</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2272,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072492</v>
+        <v>121072494</v>
       </c>
       <c r="B16" t="n">
-        <v>79683</v>
+        <v>79711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,25 +2274,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2384,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072497</v>
+        <v>121072506</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,34 +2390,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545823</v>
+        <v>545865</v>
       </c>
       <c r="R17" t="n">
-        <v>7206018</v>
+        <v>7206180</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072494</v>
+        <v>121072491</v>
       </c>
       <c r="B18" t="n">
-        <v>79711</v>
+        <v>90715</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,25 +2503,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545810</v>
+        <v>545799</v>
       </c>
       <c r="R18" t="n">
-        <v>7206003</v>
+        <v>7205964</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2603,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072489</v>
+        <v>121072492</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,21 +2619,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2643,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545766</v>
+        <v>545810</v>
       </c>
       <c r="R19" t="n">
-        <v>7205891</v>
+        <v>7206003</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072498</v>
+        <v>121072504</v>
       </c>
       <c r="B20" t="n">
-        <v>94484</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2727,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545838</v>
+        <v>545873</v>
       </c>
       <c r="R20" t="n">
-        <v>7206020</v>
+        <v>7206150</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,7 +2827,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072502</v>
+        <v>121072508</v>
       </c>
       <c r="B21" t="n">
         <v>57351</v>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545872</v>
+        <v>545887</v>
       </c>
       <c r="R21" t="n">
-        <v>7206107</v>
+        <v>7206178</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2912,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2922,7 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,10 +2944,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072505</v>
+        <v>121072502</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,34 +2960,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545867</v>
+        <v>545872</v>
       </c>
       <c r="R22" t="n">
-        <v>7206116</v>
+        <v>7206107</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,7 +3061,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072499</v>
+        <v>121072495</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545838</v>
+        <v>545810</v>
       </c>
       <c r="R23" t="n">
-        <v>7206020</v>
+        <v>7206003</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -2150,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072510</v>
+        <v>121072494</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545889</v>
+        <v>545810</v>
       </c>
       <c r="R15" t="n">
-        <v>7206177</v>
+        <v>7206003</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072494</v>
+        <v>121072506</v>
       </c>
       <c r="B16" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,38 +2274,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545810</v>
+        <v>545865</v>
       </c>
       <c r="R16" t="n">
-        <v>7206003</v>
+        <v>7206180</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072506</v>
+        <v>121072510</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,39 +2395,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545865</v>
+        <v>545889</v>
       </c>
       <c r="R17" t="n">
-        <v>7206180</v>
+        <v>7206177</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072509</v>
+        <v>121072501</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545888</v>
+        <v>545845</v>
       </c>
       <c r="R2" t="n">
-        <v>7206177</v>
+        <v>7206038</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072497</v>
+        <v>121072509</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545823</v>
+        <v>545888</v>
       </c>
       <c r="R3" t="n">
-        <v>7206018</v>
+        <v>7206177</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072488</v>
+        <v>121072508</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545768</v>
+        <v>545887</v>
       </c>
       <c r="R4" t="n">
-        <v>7205889</v>
+        <v>7206178</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072499</v>
+        <v>121072503</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545838</v>
+        <v>545872</v>
       </c>
       <c r="R5" t="n">
-        <v>7206020</v>
+        <v>7206105</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072501</v>
+        <v>121072502</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545845</v>
+        <v>545872</v>
       </c>
       <c r="R6" t="n">
-        <v>7206038</v>
+        <v>7206107</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1248,7 @@
         <v>121072500</v>
       </c>
       <c r="B7" t="n">
-        <v>90711</v>
+        <v>90723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072490</v>
+        <v>121072510</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545753</v>
+        <v>545889</v>
       </c>
       <c r="R8" t="n">
-        <v>7205958</v>
+        <v>7206177</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072505</v>
+        <v>121072498</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545867</v>
+        <v>545838</v>
       </c>
       <c r="R9" t="n">
-        <v>7206116</v>
+        <v>7206020</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072503</v>
+        <v>121072489</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545872</v>
+        <v>545766</v>
       </c>
       <c r="R10" t="n">
-        <v>7206105</v>
+        <v>7205891</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072496</v>
+        <v>121072491</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,39 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545822</v>
+        <v>545799</v>
       </c>
       <c r="R11" t="n">
-        <v>7206019</v>
+        <v>7205964</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072498</v>
+        <v>121072506</v>
       </c>
       <c r="B12" t="n">
-        <v>94484</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,38 +1817,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545838</v>
+        <v>545865</v>
       </c>
       <c r="R12" t="n">
-        <v>7206020</v>
+        <v>7206180</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072507</v>
+        <v>121072488</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,34 +1938,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545862</v>
+        <v>545768</v>
       </c>
       <c r="R13" t="n">
-        <v>7206181</v>
+        <v>7205889</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072489</v>
+        <v>121072497</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545766</v>
+        <v>545823</v>
       </c>
       <c r="R14" t="n">
-        <v>7205891</v>
+        <v>7206018</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072494</v>
+        <v>121072505</v>
       </c>
       <c r="B15" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,25 +2163,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545810</v>
+        <v>545867</v>
       </c>
       <c r="R15" t="n">
-        <v>7206003</v>
+        <v>7206116</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2225,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072506</v>
+        <v>121072492</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,39 +2279,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545865</v>
+        <v>545810</v>
       </c>
       <c r="R16" t="n">
-        <v>7206180</v>
+        <v>7206003</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2342,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072510</v>
+        <v>121072507</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545889</v>
+        <v>545862</v>
       </c>
       <c r="R17" t="n">
-        <v>7206177</v>
+        <v>7206181</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2454,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072491</v>
+        <v>121072499</v>
       </c>
       <c r="B18" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,21 +2503,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2531,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545799</v>
+        <v>545838</v>
       </c>
       <c r="R18" t="n">
-        <v>7205964</v>
+        <v>7206020</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072492</v>
+        <v>121072495</v>
       </c>
       <c r="B19" t="n">
-        <v>79683</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072504</v>
+        <v>121072494</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,25 +2723,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2755,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545873</v>
+        <v>545810</v>
       </c>
       <c r="R20" t="n">
-        <v>7206150</v>
+        <v>7206003</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2790,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072508</v>
+        <v>121072504</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,39 +2839,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545887</v>
+        <v>545873</v>
       </c>
       <c r="R21" t="n">
-        <v>7206178</v>
+        <v>7206150</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2907,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,7 +2935,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072502</v>
+        <v>121072496</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2989,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545872</v>
+        <v>545822</v>
       </c>
       <c r="R22" t="n">
-        <v>7206107</v>
+        <v>7206019</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3024,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072495</v>
+        <v>121072490</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,34 +3068,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545810</v>
+        <v>545753</v>
       </c>
       <c r="R23" t="n">
-        <v>7206003</v>
+        <v>7205958</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40733-2024 artfynd.xlsx
+++ b/artfynd/A 40733-2024 artfynd.xlsx
@@ -3055,7 +3055,7 @@
         <v>121072490</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
